--- a/MarineSABRES_SES_Shiny/Documents/Tool feedback and updates.xlsx
+++ b/MarineSABRES_SES_Shiny/Documents/Tool feedback and updates.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29523"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29728"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/85a662873548123b/Documenten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="8_{450A601D-F623-487C-9F7E-83F1E08D71C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06DFCBF0-5736-4F55-8E74-0C74E9B98D96}"/>
+  <xr:revisionPtr revIDLastSave="1370" documentId="8_{450A601D-F623-487C-9F7E-83F1E08D71C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6A4CD61-A06D-442F-8E60-F94DFD416BB1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SES tool" sheetId="1" r:id="rId1"/>
-    <sheet name="Bowtie" sheetId="2" r:id="rId2"/>
+    <sheet name="SES tool updated" sheetId="4" r:id="rId2"/>
+    <sheet name="Bowtie" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="258">
   <si>
     <t xml:space="preserve">Development </t>
   </si>
@@ -48,6 +49,9 @@
     <t>Comments</t>
   </si>
   <si>
+    <t>EG</t>
+  </si>
+  <si>
     <t>Save project</t>
   </si>
   <si>
@@ -69,12 +73,18 @@
     <t>DAPSIWRM misses W and M in title, and m in explanation</t>
   </si>
   <si>
+    <t>M is missing in title and explanion  in the beginers quick start guide</t>
+  </si>
+  <si>
     <t>Change order</t>
   </si>
   <si>
     <t>Reverse understanding and what you can do with this tool</t>
   </si>
   <si>
+    <t>Logical gap between Marine Sabres description and steps, sugestion would be DAPSIWRM  cocept expalanation, then steps</t>
+  </si>
+  <si>
     <t>General</t>
   </si>
   <si>
@@ -84,6 +94,9 @@
     <t>Change tool name from MarineSABRES to more general (e.g. SES tool)</t>
   </si>
   <si>
+    <t>Marine Sabres is not fully displayed, half of the text is hidden befind the top bar</t>
+  </si>
+  <si>
     <t>User manual</t>
   </si>
   <si>
@@ -105,6 +118,9 @@
     <t>When restarting the tool, some things remain saved whilst others do not. For example, the experience level at ‘beginner’ is still in place, whilst the filled in data for the guided pathway disappeared.</t>
   </si>
   <si>
+    <t>Indeed, that's true</t>
+  </si>
+  <si>
     <t>About'</t>
   </si>
   <si>
@@ -129,18 +145,27 @@
     <t>pending(Noorwegian partly implementd)</t>
   </si>
   <si>
+    <t>True, only top and left menu are available in Norvegian, the rest in English</t>
+  </si>
+  <si>
     <t>Auto-save</t>
   </si>
   <si>
     <t>Auto-save is disabled as a default mode. If you go to settings, there is an option to turn the autosave on and off, but off is the default mode. It says there is a risk of overwriting the data.</t>
   </si>
   <si>
+    <t>The autosave functionality has been rworked totally, making it less intrusive, but more functional</t>
+  </si>
+  <si>
     <t>Progress saved</t>
   </si>
   <si>
     <t>When clicking previous page browser, something is saved ('load saved' it says), but we cannot find this option. Also, progress is saved between tabs, but when refreshing the website, all progress is lost.</t>
   </si>
   <si>
+    <t>True, for me the same as Vivien indicated</t>
+  </si>
+  <si>
     <t>Experience level</t>
   </si>
   <si>
@@ -165,12 +190,18 @@
     <t>I have added tooltips for all menu options, need to discuss the best way simplifying the language with Gemma</t>
   </si>
   <si>
+    <t xml:space="preserve">The terminology is not changed yet </t>
+  </si>
+  <si>
     <t>Content menu</t>
   </si>
   <si>
     <t>Still quite some content left menu (in beginner's mode) -&gt; do we want stakeholders to use all of these? What I also thought about: do we want them to use the loop detection and leverage point analysis, besides the guided pathway, AI-guided SES creation, and SES visualisation?</t>
   </si>
   <si>
+    <t>Discussion it is possible to remove the loop detection and leverage point analysis from beginner's level</t>
+  </si>
+  <si>
     <t>Question box</t>
   </si>
   <si>
@@ -189,6 +220,9 @@
     <t>Prepare report does not work</t>
   </si>
   <si>
+    <t>partially fixed: generating html report, pdf is generated, but with mistakes, word and powerpoint reports are generated but shows insecure file download</t>
+  </si>
+  <si>
     <t>When trying to save the project, file cannot be downloaded at first, because it indicates 'unsafe download blocked'.</t>
   </si>
   <si>
@@ -216,6 +250,9 @@
     <t>EP0 and EP1: still can only select one option.</t>
   </si>
   <si>
+    <t xml:space="preserve">fixed, multiply options </t>
+  </si>
+  <si>
     <t>EP3</t>
   </si>
   <si>
@@ -234,6 +271,9 @@
     <t>Options start flickering and screen is blocked for a while</t>
   </si>
   <si>
+    <t>Stongly pronounced</t>
+  </si>
+  <si>
     <t>AI-guided SES creation</t>
   </si>
   <si>
@@ -246,6 +286,9 @@
     <t>indeed previous is not working, program closes</t>
   </si>
   <si>
+    <t>Still is not working</t>
+  </si>
+  <si>
     <t>Other</t>
   </si>
   <si>
@@ -268,6 +311,9 @@
   </si>
   <si>
     <t>The AI gives double suggestions (trawl fishing and trawling, or economic decline and economic loss). This might be confusing, and if you enter all of them, you will have to approve a lot of connections in the final step.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Synonyms are removed </t>
   </si>
   <si>
     <t>Disconnected</t>
@@ -297,6 +343,12 @@
     <t>Approve all button (for reviewing connections) below does not work. You have to go all the way to the top and click 'approve all' there for it to work.</t>
   </si>
   <si>
+    <t>Amend Button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove the amend button from the review of connections - this was creating a bug. Only include approve and reject so the user does not have to undertake a double action to review the connections. </t>
+  </si>
+  <si>
     <t>SES visualization</t>
   </si>
   <si>
@@ -357,6 +409,355 @@
     <t xml:space="preserve">use this link </t>
   </si>
   <si>
+    <t>Commented by</t>
+  </si>
+  <si>
+    <t>Date of comment</t>
+  </si>
+  <si>
+    <t>Fixed? (yes/no)</t>
+  </si>
+  <si>
+    <t>Date of update</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MarineSABRES is not fully displayed, half of the text is hidden.
+ It shows only when pressed. </t>
+  </si>
+  <si>
+    <t>VL</t>
+  </si>
+  <si>
+    <t>Main/opening page</t>
+  </si>
+  <si>
+    <t>When the main/opening page is firstly openened, the content menu is folded (only emojis are shown), it should show descriptions aswell (the content menu should be unfolded at the very beginning). 
+Menu button should be folded out automatically.</t>
+  </si>
+  <si>
+    <t>VP</t>
+  </si>
+  <si>
+    <t>When restarting the tool, some things remain saved whilst others 
+do not. For example, the experience level at ‘beginner’ is still in 
+place, whilst the filled in data for the guided pathway disappeared.</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>When changing the language, the language on other devices in 
+the same room change as well.</t>
+  </si>
+  <si>
+    <t>When language from English was changed to Italian and then back
+to English, not everything is changed back.</t>
+  </si>
+  <si>
+    <t>When language is selected other than English, not everything is
+actually in that language (Italian). For ex., when approving the 
+connections, they were in English, even when selected language 
+was Italian.</t>
+  </si>
+  <si>
+    <t>If in the middle of SES creation language is changed,
+everything starts from the beginning and no progress is saved.</t>
+  </si>
+  <si>
+    <t>In the language options the following languages are still missing: 
+Norwegian (PRIORITY), Greek, Polish, Dutch, Finnish</t>
+  </si>
+  <si>
+    <t>Translation in Spanish is not complete. Quite a lot of terms are in
+English. E.g. Questions are translated, but answers not.</t>
+  </si>
+  <si>
+    <t>Auto save</t>
+  </si>
+  <si>
+    <t>Auto-save is disabled as a default mode. If you go to settings, 
+there is an option to turn the autosave on and off, but off is 
+the default mode.</t>
+  </si>
+  <si>
+    <t>in the middle of the process, auto svae disable itself.</t>
+  </si>
+  <si>
+    <t>When clicking previous page browser, something is saved 
+('load saved' it says), but we cannot find this option. Also, progress
+ is saved between tabs, but when refreshing the website, 
+all progress is lost.</t>
+  </si>
+  <si>
+    <t>Terminology in general needs to be changed 
+(e.g. DAPSIWRM, leverage point analysis, etc.)</t>
+  </si>
+  <si>
+    <t>partially fixed: generating html report, pdf is generated, but with 
+mistakes, word and powerpoint reports are generated but shows 
+insecure file download.</t>
+  </si>
+  <si>
+    <t>Kick-out</t>
+  </si>
+  <si>
+    <t>Sometimes it still kicks you out, and you have to start completely
+from the beginning.</t>
+  </si>
+  <si>
+    <t>When trying to save the project, file cannot be downloaded 
+at first, because it indicates 'unsafe download blocked'.</t>
+  </si>
+  <si>
+    <t>When saving project on computer, it is saved as an RDS file. 
+This file format cannot be found when trying to import it.</t>
+  </si>
+  <si>
+    <t>People working on Macbooks have more general issues with the 
+tools, that people working on other devices do not.</t>
+  </si>
+  <si>
+    <t>Prepare report &amp;
+save project</t>
+  </si>
+  <si>
+    <t>“Prepare report” and “save project” buttons don’t work.</t>
+  </si>
+  <si>
+    <t>Save process</t>
+  </si>
+  <si>
+    <t>If you go out the page, everything gets lost. "Save the process" 
+doesn't work.</t>
+  </si>
+  <si>
+    <t>Save progress</t>
+  </si>
+  <si>
+    <t>Server is sometimes unavailable or suddenly disconnects. The 
+disconnection suddenly happened for everyone. There should be
+a button to save the progress during.</t>
+  </si>
+  <si>
+    <t>Interconnection</t>
+  </si>
+  <si>
+    <t>When connecting to the same wifi, if auto saved is disconnected, the info from ohter computers interconnects and changes your info to somebodies else.</t>
+  </si>
+  <si>
+    <t>Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It'd be good to make a possibility to have your own account,
+ so you would have all your data saved there. </t>
+  </si>
+  <si>
+    <t>Options start flickering and screen is blocked for a while.</t>
+  </si>
+  <si>
+    <t>Review suggested connections in SES creation takes some time to 
+load. Maybe we could insert a progress bar (loading ...)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidence level </t>
+  </si>
+  <si>
+    <t>For in beginner mode, maybe 'confidence’ level is redundant. 
+For experts, they might want to indicate this, but for beginners, 
+usually their knowledge is reliant on what they observe. Therefore, 
+confidence level is subjective and irrelevant for them (or for us).</t>
+  </si>
+  <si>
+    <t>Elements</t>
+  </si>
+  <si>
+    <t>While choosing elements, if you want to choose more then one,
+after choosing the first one (which only needs to be pressed once), 
+others need to be pressed two times.</t>
+  </si>
+  <si>
+    <t>Elements &amp; AI</t>
+  </si>
+  <si>
+    <t>When you choose some of the elements, further options are not
+always logical. E.g. If you choose ‘rocky shore’ and later have to 
+choose pressures etc, they're not always applicable options.</t>
+  </si>
+  <si>
+    <t>There are a lot of terms with "loss", that can cause double
+negatives, e.g. inocme loss, biodiversity loss.</t>
+  </si>
+  <si>
+    <t>When an element is picked, it can't be deselected later in reviewing</t>
+  </si>
+  <si>
+    <t>when you’re selecting activities, drivers, pressures etc, it should be
+ written that you should choose 2 or 3 options for most sufficient 
+network. It’d be amazing if you would be disabled to choose just 
+one or more than 3, and when you press “continue” it would say: 
+impossible to continue, because you need more/less options to
+ choose.</t>
+  </si>
+  <si>
+    <t>Connection approval</t>
+  </si>
+  <si>
+    <t>when choosing effects: wheter it increses/decreses, when you put 
+your mouse on the +/- button, it should show an info box, what 
+that button does.</t>
+  </si>
+  <si>
+    <t>The lowest button "approve all" doesn't work.</t>
+  </si>
+  <si>
+    <t>When you're approving connections, and approve lower ones, the 
+page goes up, and to approve the later ones, you have to scroll 
+down again.</t>
+  </si>
+  <si>
+    <t>Ecosystems services – welfare connection: AI gives all oposite signs
+(increase/decrease), and other connections after also not logical.</t>
+  </si>
+  <si>
+    <t>If you select "accept all" above, then connections you have
+amended go back to their original state (strenght:3, confidence: 3)</t>
+  </si>
+  <si>
+    <t>The first 2 connection groups give all postive effects, and all other
+are negative. Matbe automatically all should be postive, or
+AI would choose logically which are which.</t>
+  </si>
+  <si>
+    <t>There should be an option to switch order of impact effect, 
+(eg. A increases B, or B increases A)</t>
+  </si>
+  <si>
+    <t>Connection approval 
+(buttons)</t>
+  </si>
+  <si>
+    <t>The button at the very end "continue and finish" is shown always,
+even when you just approved one connections, perhaps it should
+only appear when you come to the end of all connections approving.</t>
+  </si>
+  <si>
+    <t>Connection approval
+and AI</t>
+  </si>
+  <si>
+    <t>What is happening when you change confidence? 
+How does AI system intgrate this?</t>
+  </si>
+  <si>
+    <t>Connecion approval</t>
+  </si>
+  <si>
+    <t>It’s lagging!!! When you’re approving the connections, 
+its starts glitching and the buttons start blinking.</t>
+  </si>
+  <si>
+    <t>on the side information, if there is info that you cant click on,
+ it should be left out. Cause its too much.</t>
+  </si>
+  <si>
+    <t>Leverage points</t>
+  </si>
+  <si>
+    <t>it was thought that maximum score is 5, but then 5.11 score was
+seen. What is the maximum score?</t>
+  </si>
+  <si>
+    <t>Going back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Going back button is needed. </t>
+  </si>
+  <si>
+    <t>You practically can go back, but afterwards, you have to press 
+"continue" multiple times, the other connections should be saved, 
+and it should be possible to come back were you finished,
+before coming back.</t>
+  </si>
+  <si>
+    <t>Button ''Previous''</t>
+  </si>
+  <si>
+    <t>Button '' Previous is needed for going back a step.</t>
+  </si>
+  <si>
+    <t>Quick save &amp; save as</t>
+  </si>
+  <si>
+    <t>There should be a “quick save” and “save as” buttons and it should 
+show you were it is saved.</t>
+  </si>
+  <si>
+    <t>There are no options to change the SES/CLD. When will those be 
+implemented?</t>
+  </si>
+  <si>
+    <t>Network adjustements</t>
+  </si>
+  <si>
+    <t>It would be great, if on already made network you could make
+adjustments. You could change the strenght directly on the net.
+And also, if you could two screens side by side, and if you changed
+one element and could compare how the network chenged,
+when you chnage the element or the streght.</t>
+  </si>
+  <si>
+    <t>Loops and connections</t>
+  </si>
+  <si>
+    <t>Sometimes elements in the network are left without connections.
+It'd be great, if adding or deleting loops on the network manually 
+was an option.</t>
+  </si>
+  <si>
+    <t>The arrows showing the connections: a thick arrow should show 
+strong impact, and a thin - weak. Now it is the opposite.</t>
+  </si>
+  <si>
+    <t>Screen of the network</t>
+  </si>
+  <si>
+    <t>Could be good, that there would be an option to freeze the screen,
+after some positions adjustements, since sometimes if you go and do other analysis, the network postition changes again.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save option </t>
+  </si>
+  <si>
+    <t>The network should be able to download as an image.</t>
+  </si>
+  <si>
+    <t>Loop detection</t>
+  </si>
+  <si>
+    <t>Loop count</t>
+  </si>
+  <si>
+    <t>It is possible to only show main connections network, it also would
+be good to add the loop count of the main connections</t>
+  </si>
+  <si>
+    <t>Loop detection colors</t>
+  </si>
+  <si>
+    <t>Not always loops are in different colours, they not always show
+which gives increasing and wich decreasing effect</t>
+  </si>
+  <si>
+    <t>You can download loop analysis of the Tuscany example file, 
+but not of the other templates.</t>
+  </si>
+  <si>
+    <t>Report</t>
+  </si>
+  <si>
+    <t>Stakeholder data?</t>
+  </si>
+  <si>
     <t>Bowtie</t>
   </si>
   <si>
@@ -378,6 +779,12 @@
     <t>If you forget to fill in something and go to the next step, the server disconnects and you will have to start over. Maybe system can indicate itself when user forgot to fill out necessary information.</t>
   </si>
   <si>
+    <t>Location templates</t>
+  </si>
+  <si>
+    <t>Have location-specific templates for each case ready for upload</t>
+  </si>
+  <si>
     <t>Guided creation</t>
   </si>
   <si>
@@ -412,9 +819,6 @@
   </si>
   <si>
     <t>Escalation factors</t>
-  </si>
-  <si>
-    <t>For escalation factors there is no library - you can only select your own terms. A library with some answers (and also the option to enter your own) would be nice.</t>
   </si>
   <si>
     <t>Link connections</t>
@@ -493,7 +897,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -521,6 +925,27 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -556,7 +981,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -569,23 +994,40 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Įprastas" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -863,17 +1305,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F64"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:G65"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="207.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.140625" style="3" customWidth="1"/>
     <col min="3" max="3" width="9.42578125" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="D1" t="s">
         <v>0</v>
       </c>
@@ -883,577 +1325,687 @@
       <c r="F1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="13" t="s">
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="12" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="14.45">
+      <c r="A2" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+    </row>
+    <row r="3" spans="1:7" ht="14.45">
+      <c r="A3" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B4" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="G5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:7" ht="14.45">
+      <c r="A8" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
+      <c r="C9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="1" t="s">
+    </row>
+    <row r="10" spans="1:7" ht="30.75">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="G10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="60.75">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="45.75">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="45.75">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" s="4" customFormat="1" ht="30.75">
+      <c r="A14" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="4" customFormat="1" ht="30.75">
+      <c r="A15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="45.75">
+      <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="4" customFormat="1" ht="45.75">
+      <c r="A17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="45.75">
+      <c r="A18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="4" customFormat="1" ht="30.75">
+      <c r="A20" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="76.5">
+      <c r="A21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="30.75">
+      <c r="A22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="30.75">
+      <c r="A23" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="4" customFormat="1">
+      <c r="A24" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="30.75">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="30.75">
+      <c r="A26" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="30.75">
+      <c r="A27" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F27" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="14.45">
+      <c r="A29" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="B30" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C30" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="2" t="s">
+      <c r="G31" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="30.75">
+      <c r="A32" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" t="s">
         <v>22</v>
       </c>
-      <c r="B13" t="s">
+      <c r="G32" t="s">
         <v>23</v>
       </c>
-      <c r="D13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="4" customFormat="1">
-      <c r="A14" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" s="4" customFormat="1">
-      <c r="A15" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" s="4" customFormat="1">
-      <c r="A17" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" s="4" customFormat="1">
-      <c r="A20" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="28.9">
-      <c r="A21" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" s="4" customFormat="1">
-      <c r="A24" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" t="s">
-        <v>3</v>
-      </c>
-      <c r="B25" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" t="s">
-        <v>54</v>
-      </c>
-      <c r="F27" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30" s="1" t="s">
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" s="4" customFormat="1">
+      <c r="A34" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="14.45">
+      <c r="A36" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="B37" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" t="s">
-        <v>57</v>
-      </c>
-      <c r="B31" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" t="s">
-        <v>60</v>
-      </c>
-      <c r="C32" t="s">
-        <v>17</v>
-      </c>
-      <c r="D32" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" t="s">
-        <v>61</v>
-      </c>
-      <c r="B33" t="s">
-        <v>62</v>
-      </c>
-      <c r="C33" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" s="4" customFormat="1">
-      <c r="A34" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="C37" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" s="4" customFormat="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" s="4" customFormat="1">
       <c r="A38" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>67</v>
+        <v>79</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>80</v>
       </c>
       <c r="C38" s="5"/>
       <c r="F38" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>81</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="30.75">
       <c r="A39" t="s">
-        <v>69</v>
-      </c>
-      <c r="B39" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <v>83</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="30.75">
       <c r="A40" t="s">
-        <v>71</v>
-      </c>
-      <c r="B40" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="28.9">
+        <v>85</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="60.75">
       <c r="A41" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="60.75">
       <c r="A42" t="s">
-        <v>75</v>
-      </c>
-      <c r="B42" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" s="4" customFormat="1" ht="57.6">
-      <c r="A43" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" s="4" customFormat="1">
-      <c r="A44" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" s="4" customFormat="1">
-      <c r="A45" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" s="4" customFormat="1">
-      <c r="A46" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="B48" s="12"/>
-      <c r="C48" s="12"/>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B49" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G42" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="121.5">
+      <c r="A43" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D43" t="s">
+        <v>22</v>
+      </c>
+      <c r="G43" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="30.75">
+      <c r="A44" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D44" t="s">
+        <v>22</v>
+      </c>
+      <c r="G44" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="45.75">
+      <c r="A45" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G45" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="45.75">
+      <c r="A46" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D46" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="45.75">
+      <c r="A47" t="s">
+        <v>100</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G47" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="14.45">
+      <c r="A49" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B49" s="19"/>
+      <c r="C49" s="19"/>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="B50" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" t="s">
-        <v>86</v>
-      </c>
-      <c r="B50" t="s">
-        <v>87</v>
-      </c>
-      <c r="D50" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
+      <c r="C50" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="45.75">
       <c r="A51" t="s">
-        <v>88</v>
-      </c>
-      <c r="B51" t="s">
-        <v>89</v>
+        <v>103</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="D51" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" s="4" customFormat="1">
-      <c r="A52" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
+        <v>22</v>
+      </c>
+      <c r="G51" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="45.75">
+      <c r="A52" t="s">
+        <v>105</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D52" t="s">
+        <v>22</v>
+      </c>
+      <c r="G52" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>92</v>
-      </c>
-      <c r="B53" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" s="4" customFormat="1">
-      <c r="A54" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
+        <v>107</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D53" t="s">
+        <v>22</v>
+      </c>
+      <c r="G53" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="30.75">
+      <c r="A54" t="s">
+        <v>109</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="30.75">
       <c r="A55" t="s">
-        <v>96</v>
-      </c>
-      <c r="B55" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="B57" s="12"/>
-      <c r="C57" s="12"/>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B58" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D55" t="s">
+        <v>22</v>
+      </c>
+      <c r="G55" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>113</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G56" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="14.45">
+      <c r="A58" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B58" s="19"/>
+      <c r="C58" s="19"/>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="B59" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" t="s">
-        <v>99</v>
-      </c>
-      <c r="B59" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
+      <c r="C59" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="30.75">
       <c r="A60" t="s">
-        <v>101</v>
-      </c>
-      <c r="B60" t="s">
-        <v>102</v>
-      </c>
-      <c r="D60" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B62" s="12"/>
-      <c r="C62" s="12"/>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B63" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="30.75">
+      <c r="A61" t="s">
+        <v>118</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D61" t="s">
+        <v>22</v>
+      </c>
+      <c r="G61" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="14.45">
+      <c r="A63" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B63" s="19"/>
+      <c r="C63" s="19"/>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="B64" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" t="s">
-        <v>103</v>
-      </c>
-      <c r="B64" t="s">
-        <v>104</v>
-      </c>
-      <c r="D64" t="s">
-        <v>18</v>
+      <c r="C64" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" t="s">
+        <v>120</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D65" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A58:C58"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A29:C29"/>
@@ -1465,8 +2017,828 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B2EBAE3-B488-49B5-9F35-D8B40B713F4A}">
+  <dimension ref="A1:G69"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="2" max="2" width="57.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="45.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30.75">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" s="14"/>
+    </row>
+    <row r="4" spans="1:7" ht="74.25" customHeight="1">
+      <c r="A4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D4" s="14">
+        <v>46036</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="46.5" customHeight="1">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5" s="14"/>
+    </row>
+    <row r="6" spans="1:7" ht="30.75">
+      <c r="A6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="14"/>
+    </row>
+    <row r="7" spans="1:7" ht="33.75" customHeight="1">
+      <c r="A7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" s="14">
+        <v>46036</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="60.75">
+      <c r="A8" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D8" s="14">
+        <v>46036</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="30.75">
+      <c r="A9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" s="14">
+        <v>46036</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="30.75">
+      <c r="A10" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D10" s="14"/>
+    </row>
+    <row r="11" spans="1:7" ht="30.75">
+      <c r="A11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D11" s="14">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="45.75">
+      <c r="A12" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D13" s="14">
+        <v>46048</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="62.25" customHeight="1">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C14" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30.75">
+      <c r="A15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C15" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="47.25" customHeight="1">
+      <c r="A16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="33.75" customHeight="1">
+      <c r="A17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C17" t="s">
+        <v>130</v>
+      </c>
+      <c r="D17" s="14">
+        <v>46036</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="30.75">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="30.75">
+      <c r="A19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C19" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="30.75">
+      <c r="A20" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C20" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="30.75">
+      <c r="A21" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="C21" t="s">
+        <v>130</v>
+      </c>
+      <c r="D21" s="14">
+        <v>46036</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="30.75">
+      <c r="A22" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="C22" t="s">
+        <v>130</v>
+      </c>
+      <c r="D22" s="14">
+        <v>46036</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="45.75">
+      <c r="A23" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="C23" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23" s="14">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="45.75">
+      <c r="A24" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C24" t="s">
+        <v>130</v>
+      </c>
+      <c r="D24" s="14">
+        <v>46049</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="30.75">
+      <c r="A25" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" t="s">
+        <v>130</v>
+      </c>
+      <c r="D25" s="14">
+        <v>46063</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" t="s">
+        <v>160</v>
+      </c>
+      <c r="C28" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="30.75">
+      <c r="A31" t="s">
+        <v>85</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C31" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="62.25" customHeight="1">
+      <c r="A32" t="s">
+        <v>162</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C32" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="46.5" customHeight="1">
+      <c r="A33" t="s">
+        <v>164</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C33" t="s">
+        <v>130</v>
+      </c>
+      <c r="D33" s="14">
+        <v>46036</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="46.5" customHeight="1">
+      <c r="A34" t="s">
+        <v>166</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C34" t="s">
+        <v>130</v>
+      </c>
+      <c r="D34" s="14">
+        <v>46036</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="33" customHeight="1">
+      <c r="A35" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C35" t="s">
+        <v>127</v>
+      </c>
+      <c r="D35" s="14">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="33" customHeight="1">
+      <c r="A36" t="s">
+        <v>164</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C36" t="s">
+        <v>130</v>
+      </c>
+      <c r="D36" s="14">
+        <v>46044</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="90" customHeight="1">
+      <c r="A37" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C37" t="s">
+        <v>130</v>
+      </c>
+      <c r="D37" s="14">
+        <v>46063</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="48" customHeight="1">
+      <c r="A38" t="s">
+        <v>171</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="C38" t="s">
+        <v>130</v>
+      </c>
+      <c r="D38" s="14">
+        <v>46036</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>171</v>
+      </c>
+      <c r="B39" t="s">
+        <v>173</v>
+      </c>
+      <c r="C39" t="s">
+        <v>130</v>
+      </c>
+      <c r="D39" s="14">
+        <v>46036</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="49.5" customHeight="1">
+      <c r="A40" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C40" t="s">
+        <v>130</v>
+      </c>
+      <c r="D40" s="14">
+        <v>46036</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="33.75" customHeight="1">
+      <c r="A41" t="s">
+        <v>171</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="C41" t="s">
+        <v>130</v>
+      </c>
+      <c r="D41" s="14">
+        <v>46036</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="33.75" customHeight="1">
+      <c r="A42" t="s">
+        <v>171</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="C42" t="s">
+        <v>127</v>
+      </c>
+      <c r="D42" s="14">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="52.5" customHeight="1">
+      <c r="A43" t="s">
+        <v>171</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="C43" t="s">
+        <v>130</v>
+      </c>
+      <c r="D43" s="14">
+        <v>46048</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="38.25" customHeight="1">
+      <c r="A44" t="s">
+        <v>171</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="C44" t="s">
+        <v>130</v>
+      </c>
+      <c r="D44" s="14">
+        <v>46049</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="61.5" customHeight="1">
+      <c r="A45" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="C45" t="s">
+        <v>130</v>
+      </c>
+      <c r="D45" s="14">
+        <v>46049</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="33.75" customHeight="1">
+      <c r="A46" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="C46" t="s">
+        <v>127</v>
+      </c>
+      <c r="D46" s="14">
+        <v>46044</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="33.75" customHeight="1">
+      <c r="A47" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="C47" t="s">
+        <v>130</v>
+      </c>
+      <c r="D47" s="14">
+        <v>46063</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="33.75" customHeight="1">
+      <c r="A48" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="C48" t="s">
+        <v>130</v>
+      </c>
+      <c r="D48" s="14">
+        <v>46063</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="33.75" customHeight="1">
+      <c r="A49" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="C49" t="s">
+        <v>127</v>
+      </c>
+      <c r="D49" s="14">
+        <v>46044</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="B50" t="s">
+        <v>189</v>
+      </c>
+      <c r="C50" t="s">
+        <v>130</v>
+      </c>
+      <c r="D50" s="14">
+        <v>46036</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="63.75" customHeight="1">
+      <c r="A51" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C51" t="s">
+        <v>130</v>
+      </c>
+      <c r="D51" s="14">
+        <v>46036</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="23.25" customHeight="1">
+      <c r="A52" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C52" t="s">
+        <v>130</v>
+      </c>
+      <c r="D52" s="14">
+        <v>46049</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="33" customHeight="1">
+      <c r="A53" t="s">
+        <v>193</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="C53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D53" s="14">
+        <v>46036</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="30.75">
+      <c r="A56" t="s">
+        <v>109</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C56" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="78.75" customHeight="1">
+      <c r="A57" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C57" t="s">
+        <v>130</v>
+      </c>
+      <c r="D57" s="14">
+        <v>46036</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="47.25" customHeight="1">
+      <c r="A58" t="s">
+        <v>198</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C58" t="s">
+        <v>130</v>
+      </c>
+      <c r="D58" s="14">
+        <v>46036</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="34.5" customHeight="1">
+      <c r="A59" t="s">
+        <v>198</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C59" t="s">
+        <v>130</v>
+      </c>
+      <c r="D59" s="14">
+        <v>46049</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="51" customHeight="1">
+      <c r="A60" t="s">
+        <v>201</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C60" t="s">
+        <v>130</v>
+      </c>
+      <c r="D60" s="14">
+        <v>46049</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="24.75" customHeight="1">
+      <c r="A61" t="s">
+        <v>203</v>
+      </c>
+      <c r="B61" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="C61" t="s">
+        <v>130</v>
+      </c>
+      <c r="D61" s="14">
+        <v>46063</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="45.75">
+      <c r="A64" t="s">
+        <v>206</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C64" t="s">
+        <v>130</v>
+      </c>
+      <c r="D64" s="14">
+        <v>46036</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="30.75">
+      <c r="A65" t="s">
+        <v>208</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="13" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="30.75">
+      <c r="A68" t="s">
+        <v>116</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C68" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
+        <v>211</v>
+      </c>
+      <c r="B69" t="s">
+        <v>212</v>
+      </c>
+      <c r="C69" t="s">
+        <v>130</v>
+      </c>
+      <c r="D69" s="14">
+        <v>46049</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C123ADB2-04E3-441A-835D-CE3A64A6D212}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="22.140625" bestFit="1" customWidth="1"/>
@@ -1474,252 +2846,266 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
+      <c r="A1" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
+      <c r="A2" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="4" customFormat="1">
       <c r="A4" s="4" t="s">
-        <v>106</v>
+        <v>214</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>107</v>
+        <v>215</v>
       </c>
       <c r="C4" s="5"/>
     </row>
     <row r="5" spans="1:3" s="4" customFormat="1" ht="15">
       <c r="A5" s="4" t="s">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>109</v>
+        <v>217</v>
       </c>
       <c r="C5" s="5"/>
     </row>
     <row r="6" spans="1:3" s="4" customFormat="1">
       <c r="A6" s="4" t="s">
-        <v>110</v>
+        <v>218</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>111</v>
+        <v>219</v>
       </c>
       <c r="C6" s="5"/>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
+    <row r="7" spans="1:3" ht="15">
+      <c r="A7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B7" t="s">
+        <v>221</v>
+      </c>
+      <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="A9" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="15">
-      <c r="A10" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15">
+      <c r="C10" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15">
+      <c r="A11" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>117</v>
+        <v>225</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>226</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15">
       <c r="A13" t="s">
-        <v>119</v>
+        <v>227</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15">
       <c r="A14" t="s">
-        <v>121</v>
+        <v>229</v>
       </c>
       <c r="B14" t="s">
-        <v>122</v>
+        <v>230</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15">
       <c r="A15" t="s">
-        <v>123</v>
+        <v>231</v>
       </c>
       <c r="B15" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15">
       <c r="A16" t="s">
-        <v>125</v>
-      </c>
-      <c r="B16" t="s">
-        <v>126</v>
+        <v>233</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>234</v>
       </c>
       <c r="B17" t="s">
-        <v>127</v>
+        <v>235</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>129</v>
+        <v>236</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>130</v>
+        <v>237</v>
       </c>
       <c r="B19" t="s">
-        <v>131</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>132</v>
+        <v>239</v>
       </c>
       <c r="B20" t="s">
-        <v>133</v>
+        <v>240</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>134</v>
+        <v>241</v>
       </c>
       <c r="B21" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>243</v>
+      </c>
+      <c r="B22" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="1" t="s">
+      <c r="A24" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" s="4" customFormat="1" ht="15">
-      <c r="A25" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="C25" s="5"/>
+      <c r="C25" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="26" spans="1:3" s="4" customFormat="1" ht="15">
-      <c r="A26" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>140</v>
+      <c r="A26" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>247</v>
       </c>
       <c r="C26" s="5"/>
     </row>
-    <row r="27" spans="1:3" s="4" customFormat="1">
-      <c r="A27" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" s="4" customFormat="1" ht="15">
+    <row r="27" spans="1:3" s="4" customFormat="1" ht="15">
+      <c r="A27" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="C27" s="5"/>
+    </row>
+    <row r="28" spans="1:3" s="4" customFormat="1">
       <c r="A28" s="4" t="s">
-        <v>143</v>
+        <v>250</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>144</v>
+        <v>251</v>
       </c>
     </row>
     <row r="29" spans="1:3" s="4" customFormat="1" ht="15">
       <c r="A29" s="4" t="s">
-        <v>145</v>
+        <v>252</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="28.9">
-      <c r="A30" t="s">
-        <v>147</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="15"/>
+        <v>253</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="4" customFormat="1" ht="15">
+      <c r="A30" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="28.9">
+      <c r="A31" t="s">
+        <v>256</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A9:C9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
